--- a/output/pdf_financials_xlsx/SURF.UN.xlsx
+++ b/output/pdf_financials_xlsx/SURF.UN.xlsx
@@ -1310,19 +1310,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>10.407</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.628</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.067</v>
       </c>
     </row>
     <row r="35">
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>10.407</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.628</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.067</v>
       </c>
     </row>
     <row r="37">
@@ -1618,19 +1618,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>11.756</v>
+        <v>1.349</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.592</v>
+        <v>3.964</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>8.257</v>
+        <v>5.317</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>9.513999999999999</v>
+        <v>7.434</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>6.885</v>
+        <v>3.818</v>
       </c>
     </row>
     <row r="49">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">

--- a/output/pdf_financials_xlsx/SURF.UN.xlsx
+++ b/output/pdf_financials_xlsx/SURF.UN.xlsx
@@ -2911,19 +2911,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>1.395</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>0.313</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.385</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>2.173</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>1.861</v>
       </c>
     </row>
     <row r="107">
@@ -9065,7 +9065,11 @@
           <t>Change in non-cash operating working capital 18(a)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -9958,7 +9962,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -9999,7 +10007,11 @@
           <t>Change in non-cash operating working capital 18(a)</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="n">
         <v>1.395</v>
       </c>
@@ -10701,7 +10713,11 @@
           <t>Change in non-cash operating working capital 20(a)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -11667,7 +11683,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E204" s="5" t="n">
         <v>0.476</v>
       </c>
@@ -11788,7 +11808,11 @@
           <t>Change in non-cash operating working capital 19(a)</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E207" s="5" t="n">
         <v>1.395</v>
       </c>
